--- a/data/cci/cci-platform.xlsx
+++ b/data/cci/cci-platform.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{68AA7177-40B0-4065-AF33-66A2695A1CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20D2E51E-9744-42BB-94C1-0C6C6B52FF64}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{68AA7177-40B0-4065-AF33-66A2695A1CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{068D19F6-9776-4CE8-B87D-EE95656EC190}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1C9BF221-BF04-2F46-91C8-1781F5B972F8}"/>
+    <workbookView xWindow="1440" yWindow="4635" windowWidth="34515" windowHeight="15285" xr2:uid="{1C9BF221-BF04-2F46-91C8-1781F5B972F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="717">
   <si>
     <t>URI</t>
   </si>
@@ -2238,6 +2238,24 @@
   <si>
     <t>plat_odin</t>
   </si>
+  <si>
+    <t>plat_himawari8</t>
+  </si>
+  <si>
+    <t>Himawari-8</t>
+  </si>
+  <si>
+    <t>plat_himawari9</t>
+  </si>
+  <si>
+    <t>Himawari-9</t>
+  </si>
+  <si>
+    <t>https://space.oscar.wmo.int/satellites/view/himawari_8</t>
+  </si>
+  <si>
+    <t>https://space.oscar.wmo.int/satellites/view/himawari_9</t>
+  </si>
 </sst>
 </file>
 
@@ -2246,7 +2264,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$£-809]#,##0.00;[Red]&quot;-&quot;[$£-809]#,##0.00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2362,6 +2380,11 @@
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3921,7 +3944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F33281D-4F86-224D-82CF-E71299C93FE7}">
-  <dimension ref="A1:E175"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -6567,7 +6590,36 @@
         <v>709</v>
       </c>
     </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
+        <v>711</v>
+      </c>
+      <c r="B176" t="s">
+        <v>712</v>
+      </c>
+      <c r="D176" t="s">
+        <v>712</v>
+      </c>
+      <c r="E176" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
+        <v>713</v>
+      </c>
+      <c r="B177" t="s">
+        <v>714</v>
+      </c>
+      <c r="D177" t="s">
+        <v>714</v>
+      </c>
+      <c r="E177" t="s">
+        <v>716</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E62" r:id="rId1" xr:uid="{CA667A1D-923E-594E-B24E-8E95613DF6D2}"/>
     <hyperlink ref="E124" r:id="rId2" xr:uid="{449FADC9-C466-3A4B-9CB7-E9128DE332EB}"/>
